--- a/product_selector_out/STM32L4x2 - diff.xlsx
+++ b/product_selector_out/STM32L4x2 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -79,6 +94,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -597,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1482</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="18">
@@ -747,22 +765,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -774,18 +792,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -797,59 +819,67 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -861,18 +891,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -884,76 +914,88 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -976,7 +1018,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -999,7 +1041,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1022,7 +1064,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1045,7 +1087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1068,7 +1110,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1091,45 +1133,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1141,76 +1179,88 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1233,7 +1283,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1256,153 +1306,169 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>15||16</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>15, 16</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15||16 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1425,7 +1491,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1448,99 +1514,115 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1563,7 +1645,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1586,80 +1668,88 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1682,7 +1772,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1705,87 +1795,99 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1797,18 +1899,18 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -1820,101 +1922,1313 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>STM32L422CB</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32L422CB</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32L422CB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32L452CE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32L452CE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L452CE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L452CE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L452CE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32L422RB</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32L422RB</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32L422RB</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L422RB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L422RB</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L422RB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L412RB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L412RB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32L452CC</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L452CC</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L452CC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L452CC</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L452CC</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L412K8</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32L412K8</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32L412TB</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32L412TB</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32L432KC</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>STM32L422TB</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E72"/>
+  <autoFilter ref="A18:E120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x2 - diff.xlsx
+++ b/product_selector_out/STM32L4x2 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -86,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,7 +91,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -565,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -635,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1466</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="18">
@@ -846,22 +840,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -873,13 +863,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -891,23 +881,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L422KB</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -932,9 +926,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -951,7 +945,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -959,9 +953,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -973,22 +967,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1000,13 +990,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1018,18 +1008,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1046,13 +1036,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1064,18 +1054,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1092,13 +1082,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1110,18 +1100,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1138,13 +1128,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1156,23 +1146,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1197,9 +1191,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1224,9 +1218,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1238,22 +1232,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1265,13 +1255,13 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1283,23 +1273,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1324,9 +1318,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1337,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1351,9 +1345,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1359,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>15||16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1391,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15||16</t>
+          <t>15, 16</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1405,9 +1399,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1418,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>15, 16</t>
+          <t>15||16 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1432,9 +1426,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1440,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>15||16 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1473,13 +1463,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1491,23 +1481,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1532,9 +1526,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1545,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1559,9 +1553,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1573,22 +1567,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1600,68 +1590,72 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1672,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1686,9 +1680,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1700,22 +1694,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1727,68 +1717,72 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1799,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1813,9 +1807,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1827,22 +1821,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1854,68 +1844,72 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1926,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1940,9 +1934,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1954,22 +1948,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1981,95 +1971,99 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2081,22 +2075,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2108,29 +2098,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2140,63 +2126,71 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2208,22 +2202,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2235,163 +2225,163 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2408,83 +2398,71 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2507,7 +2485,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2530,87 +2508,99 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -2627,29 +2617,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2667,16 +2653,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2686,7 +2672,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2694,43 +2680,43 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2753,7 +2739,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2776,7 +2762,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2803,7 +2789,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2830,7 +2816,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2857,7 +2843,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2880,7 +2866,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2903,61 +2889,53 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2967,70 +2945,78 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3053,7 +3039,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3073,162 +3059,8 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32L422TB</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E120"/>
+  <autoFilter ref="A18:E114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x2 - diff.xlsx
+++ b/product_selector_out/STM32L4x2 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1536</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1472</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="18">
@@ -881,27 +881,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -926,9 +922,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -945,7 +941,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -953,9 +949,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -967,18 +963,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -990,13 +990,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1008,18 +1008,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1031,18 +1031,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1146,54 +1146,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1202,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1218,9 +1210,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1232,18 +1224,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1255,99 +1251,91 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1359,17 +1347,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>15||16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1386,17 +1374,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15, 16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -1413,17 +1401,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>15||16 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1440,18 +1428,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>15||16</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1463,117 +1455,113 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>15, 16</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15||16 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1590,25 +1578,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1626,16 +1618,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1645,7 +1637,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1653,54 +1645,50 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -1712,18 +1700,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -1735,7 +1723,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1762,7 +1750,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1789,7 +1777,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1816,7 +1804,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1839,7 +1827,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1862,34 +1850,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1899,24 +1883,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1926,58 +1910,62 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1989,61 +1977,53 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2053,231 +2033,239 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2289,61 +2277,53 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2353,70 +2333,78 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2439,7 +2427,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2462,18 +2450,18 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2485,18 +2473,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -2508,34 +2496,30 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2553,16 +2537,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2572,7 +2556,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2580,50 +2564,54 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -2635,99 +2623,87 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -2739,18 +2715,18 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -2762,34 +2738,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2807,16 +2779,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2826,7 +2798,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2834,50 +2806,54 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -2889,18 +2865,18 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -2912,18 +2888,18 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -2935,7 +2911,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2945,12 +2921,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -2962,7 +2938,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2972,12 +2948,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -2989,7 +2965,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2999,12 +2975,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3016,7 +2992,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3039,7 +3015,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3059,8 +3035,377 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32L452RC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32L452VC</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32L412CB</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32L422TB</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E114"/>
+  <autoFilter ref="A18:E129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>